--- a/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/site_eval_heldout.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/site_eval_heldout.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,20 +461,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Prob_Cluster 3</t>
+          <t>p_max</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>p_max</t>
+          <t>delta_p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>delta_p</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
@@ -483,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>011A</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -495,24 +490,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3176148436405246</v>
+        <v>0.9299576344919035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1811130916664437</v>
+        <v>0.07004236550809655</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5012720646930319</v>
+        <v>0.9299576344919035</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5012720646930319</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.1836572210525073</v>
-      </c>
-      <c r="J2" t="inlineStr">
+        <v>0.859915268983807</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -521,11 +513,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>016C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -533,24 +525,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0949971454274436</v>
+        <v>0.9993622045626561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.727318946080999</v>
+        <v>0.0006377954373438754</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1776839084915574</v>
+        <v>0.9993622045626561</v>
       </c>
       <c r="H3" t="n">
-        <v>0.727318946080999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5496350375894417</v>
-      </c>
-      <c r="J3" t="inlineStr">
+        <v>0.9987244091253122</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -559,11 +548,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -571,24 +560,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2660409444042317</v>
+        <v>0.4691515306543105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2529121437324889</v>
+        <v>0.5308484693456895</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4810469118632794</v>
+        <v>0.5308484693456895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4810469118632794</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.2150059674590477</v>
-      </c>
-      <c r="J4" t="inlineStr">
+        <v>0.06169693869137904</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -597,7 +583,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -605,28 +591,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3896606123821995</v>
+        <v>0.7414357911807732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2440776386220998</v>
+        <v>0.2585642088192268</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3662617489957007</v>
+        <v>0.7414357911807732</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3896606123821995</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.02339886338649877</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>0.4828715823615464</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -635,7 +618,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -650,21 +633,18 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4077606766448914</v>
+        <v>0.9999440410900682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2020798741012985</v>
+        <v>5.595890993180852e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3901594492538101</v>
+        <v>0.9999440410900682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4077606766448914</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01760122739108122</v>
-      </c>
-      <c r="J6" t="inlineStr">
+        <v>0.9998880821801364</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -673,7 +653,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -681,28 +661,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.159703111482533</v>
+        <v>0.9989943957712283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1699545567141592</v>
+        <v>0.001005604228771741</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6703423318033078</v>
+        <v>0.9989943957712283</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6703423318033078</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5003877750891487</v>
-      </c>
-      <c r="J7" t="inlineStr">
+        <v>0.9979887915424566</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -711,36 +688,33 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1511819584531801</v>
+        <v>0.1055665081894095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3872710889604491</v>
+        <v>0.8944334918105905</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4615469525863707</v>
+        <v>0.8944334918105905</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4615469525863707</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.07427586362592165</v>
-      </c>
-      <c r="J8" t="inlineStr">
+        <v>0.788866983621181</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -749,11 +723,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -761,24 +735,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2974565370270606</v>
+        <v>0.9955948267580035</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1373959568691734</v>
+        <v>0.004405173241996495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5651475061037661</v>
+        <v>0.9955948267580035</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5651475061037661</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.2676909690767055</v>
-      </c>
-      <c r="J9" t="inlineStr">
+        <v>0.991189653516007</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -787,7 +758,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -795,28 +766,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2008009003661782</v>
+        <v>0.9995756805159539</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2549335448622857</v>
+        <v>0.0004243194840460445</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5442655547715362</v>
+        <v>0.9995756805159539</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5442655547715362</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2893320099092505</v>
-      </c>
-      <c r="J10" t="inlineStr">
+        <v>0.9991513610319078</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -825,7 +793,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -837,24 +805,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.270854089914268</v>
+        <v>0.9861343497855172</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1091819545011201</v>
+        <v>0.01386565021448284</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6199639555846119</v>
+        <v>0.9861343497855172</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6199639555846119</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.3491098656703439</v>
-      </c>
-      <c r="J11" t="inlineStr">
+        <v>0.9722686995710343</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -863,11 +828,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -875,24 +840,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3584544258590445</v>
+        <v>0.9287319927167482</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1509766326555023</v>
+        <v>0.07126800728325182</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4905689414854532</v>
+        <v>0.9287319927167482</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4905689414854532</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.1321145156264086</v>
-      </c>
-      <c r="J12" t="inlineStr">
+        <v>0.8574639854334964</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -901,7 +863,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -913,24 +875,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2918710746963336</v>
+        <v>0.9974994951236491</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1216067676665235</v>
+        <v>0.00250050487635089</v>
       </c>
       <c r="G13" t="n">
-        <v>0.586522157637143</v>
+        <v>0.9974994951236491</v>
       </c>
       <c r="H13" t="n">
-        <v>0.586522157637143</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2946510829408094</v>
-      </c>
-      <c r="J13" t="inlineStr">
+        <v>0.9949989902472982</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -939,36 +898,33 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Uncertain</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1777070053380987</v>
+        <v>0.9999098663656073</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1454106028625954</v>
+        <v>9.01336343927377e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6768823917993058</v>
+        <v>0.9999098663656073</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6768823917993058</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.499175386461207</v>
-      </c>
-      <c r="J14" t="inlineStr">
+        <v>0.9998197327312146</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -977,7 +933,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -989,24 +945,21 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12991678834724</v>
+        <v>0.9400224033196544</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08847808298633889</v>
+        <v>0.05997759668034562</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7816051286664212</v>
+        <v>0.9400224033196544</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7816051286664212</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.6516883403191812</v>
-      </c>
-      <c r="J15" t="inlineStr">
+        <v>0.8800448066393087</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
@@ -1015,36 +968,383 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6208464868984618</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3791535131015383</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6208464868984618</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2416929737969235</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9994286937623832</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0005713062376168569</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9994286937623832</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9988573875247664</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>S28(5)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9999768499469999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.315005300012517e-05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9999768499469999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9999536998939997</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S51</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9977723577740212</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.002227642225978873</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9977723577740212</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9955447155480424</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9449475764078157</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.05505242359218426</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9449475764078157</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8898951528156314</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9981489581940886</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.001851041805911422</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9981489581940886</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9962979163881771</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>S54</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9698271214420378</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.03017287855796226</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9698271214420378</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9396542428840755</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>S69</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9988739190434267</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.001126080956573267</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.9988739190434267</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9977478380868534</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>S70</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7787973741044067</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2212026258955933</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7787973741044067</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5575947482088135</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>S72</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8721581738641151</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1278418261358849</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8721581738641151</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.7443163477282302</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Held-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>S74</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Uncertain</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="B26" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.161562199100788</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3159486770927346</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.5224891238064773</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5224891238064773</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.2065404467137427</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Peripheral</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9647605649643517</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.03523943503564828</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.9647605649643517</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9295211299287034</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Held-out</t>
         </is>
